--- a/artfynd/A 35622-2026 artfynd.xlsx
+++ b/artfynd/A 35622-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136194224</v>
       </c>
       <c r="B2" t="n">
-        <v>78847</v>
+        <v>78848</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136194226</v>
       </c>
       <c r="B3" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136194225</v>
       </c>
       <c r="B4" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 35622-2026 artfynd.xlsx
+++ b/artfynd/A 35622-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136194224</v>
       </c>
       <c r="B2" t="n">
-        <v>78848</v>
+        <v>78852</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136194226</v>
       </c>
       <c r="B3" t="n">
-        <v>79202</v>
+        <v>79206</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136194225</v>
       </c>
       <c r="B4" t="n">
-        <v>79203</v>
+        <v>79207</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 35622-2026 artfynd.xlsx
+++ b/artfynd/A 35622-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136194224</v>
       </c>
       <c r="B2" t="n">
-        <v>78852</v>
+        <v>78853</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136194226</v>
       </c>
       <c r="B3" t="n">
-        <v>79206</v>
+        <v>79207</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136194225</v>
       </c>
       <c r="B4" t="n">
-        <v>79207</v>
+        <v>79208</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
